--- a/tests/Fixtures/Workbooks/policy-workbook-missing-status-column.xlsx
+++ b/tests/Fixtures/Workbooks/policy-workbook-missing-status-column.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Policies" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Policy votes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Divisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Display notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Divisions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -930,6 +931,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Policy ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Party or MP</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Note (public)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test Party</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Voted for the motion but opposed its main clause.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
